--- a/test/fixtures/xlsx/invalid/invalid.xlsx
+++ b/test/fixtures/xlsx/invalid/invalid.xlsx
@@ -12,38 +12,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
-  <si>
-    <t xml:space="preserve">~~table:Catalog~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+  <si>
+    <t xml:space="preserve">:table Catalog</t>
   </si>
   <si>
     <t xml:space="preserve">Repeats a primary index value and a secondary index value.</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
     <t xml:space="preserve">*Code</t>
   </si>
   <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
     <t xml:space="preserve">secondary index</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
@@ -71,7 +80,7 @@
     <t xml:space="preserve">third</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Orders~~</t>
+    <t xml:space="preserve">:table Orders</t>
   </si>
   <si>
     <t xml:space="preserve">Points at a Catalog row that does not exist.</t>
@@ -80,15 +89,12 @@
     <t xml:space="preserve">Item</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Catalog</t>
+  </si>
+  <si>
     <t xml:space="preserve">ordered item</t>
   </si>
   <si>
-    <t xml:space="preserve">foreign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalog</t>
-  </si>
-  <si>
     <t xml:space="preserve">Qty</t>
   </si>
   <si>
@@ -101,7 +107,7 @@
     <t xml:space="preserve">99</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Shipments~~</t>
+    <t xml:space="preserve">:table Shipments</t>
   </si>
   <si>
     <t xml:space="preserve">References a table that does not exist, and a field that does not exist.</t>
@@ -110,19 +116,19 @@
     <t xml:space="preserve">Warehouse</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign NoSuchTable</t>
+  </si>
+  <si>
     <t xml:space="preserve">no such table</t>
   </si>
   <si>
-    <t xml:space="preserve">NoSuchTable</t>
-  </si>
-  <si>
     <t xml:space="preserve">CatalogLabel</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Catalog.NoSuchField</t>
+  </si>
+  <si>
     <t xml:space="preserve">no such field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalog.NoSuchField</t>
   </si>
 </sst>
 </file>
@@ -167,92 +173,146 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:N11"/>
+  <dimension ref="B2:O9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I4" t="s">
         <v>25</v>
       </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
       <c r="L4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="N4" t="s">
         <v>34</v>
       </c>
+      <c r="O4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
       </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
       <c r="L5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N5" t="s">
         <v>35</v>
       </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -260,141 +320,92 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
       <c r="G6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="J6" t="s">
+        <v>9</v>
       </c>
       <c r="L6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="O6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L7" t="s">
-        <v>5</v>
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
       </c>
       <c r="M7" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="N7" t="s">
-        <v>36</v>
+        <v>15</v>
+      </c>
+      <c r="O7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" t="s">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" t="s">
-        <v>6</v>
-      </c>
-      <c r="M8" t="s">
-        <v>6</v>
-      </c>
-      <c r="N8" t="s">
-        <v>6</v>
+        <v>30</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>12</v>
-      </c>
-      <c r="M9" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
